--- a/currentbuild/CodeSystem-no-kodeverk-7852.codesystem.xlsx
+++ b/currentbuild/CodeSystem-no-kodeverk-7852.codesystem.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/CodeSystem-no-kodeverk-7852.codesystem.xlsx
+++ b/currentbuild/CodeSystem-no-kodeverk-7852.codesystem.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.1.3</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/CodeSystem-no-kodeverk-7852.codesystem.xlsx
+++ b/currentbuild/CodeSystem-no-kodeverk-7852.codesystem.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.3</t>
+    <t>0.1.4</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/CodeSystem-no-kodeverk-7852.codesystem.xlsx
+++ b/currentbuild/CodeSystem-no-kodeverk-7852.codesystem.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.4</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/CodeSystem-no-kodeverk-7852.codesystem.xlsx
+++ b/currentbuild/CodeSystem-no-kodeverk-7852.codesystem.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
